--- a/CustomWhateverLoader/LangMod/CN/cwl_sources.xlsx
+++ b/CustomWhateverLoader/LangMod/CN/cwl_sources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpace\GameMods\Elin.Plugins\CustomWhateverLoader\LangMod\CN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B957187-17AF-4898-89B8-FA1F24EE9430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258EC457-1E06-42EB-B354-241095A5A2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10875" yWindow="2190" windowWidth="31395" windowHeight="15975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3045" yWindow="3030" windowWidth="31395" windowHeight="15975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -465,6 +465,244 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>cwl_log_mat_color</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>added material color {0}, main {1}, alt {2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_warn_mat_color</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>failed to add material color {0}, {1}
+{2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无法添加材质颜色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> {0}, {1}
+{2}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">新增材质颜色 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">{0}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> {1}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>副</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> {2}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_warn_decltype_missing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无法查询MOD声明类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">: {0}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或许它未能加载或缺少（传递）依赖项</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">这并不是一个 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">CWL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>异常并且可以忽略</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>one of the {0} {1} processors failed, the exception has been ignored
+{2}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_warn_processor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">一个 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">{0} {1} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处理失败</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已忽略异常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+{2}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_log_ele_gain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="15.8"/>
@@ -472,15 +710,15 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>无法添加物品</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> {0} </t>
+      <t>工作表缺失对应缺省值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
     </r>
     <r>
       <rPr>
@@ -489,15 +727,23 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> {1},  </t>
+      <t>行3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -506,246 +752,40 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>物品无法生成</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_log_mat_color</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>added material color {0}, main {1}, alt {2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_warn_mat_color</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>failed to add material color {0}, {1}
-{2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无法添加材质颜色</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> {0}, {1}
-{2}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">新增材质颜色 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{0}, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>主</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> {1}, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>副</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> {2}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_warn_decltype_missing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无法查询MOD声明类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">: {0}, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或许它未能加载或缺少（传递）依赖项</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">  
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">这并不是一个 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">CWL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>异常并且可以忽略</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>one of the {0} {1} processors failed, the exception has been ignored
-{2}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_warn_processor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">一个 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">{0} {1} </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>处理失败</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>已忽略异常</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-{2}</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_log_ele_gain</t>
+      <t>或许不兼容此版本</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>this is the last time CWL warns about it, the rest will be silently ignored to reduce log spam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_warn_empty_default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheet is missing default entries (3rd row) and might be incompatible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_warn_stock_file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_log_post_cleanup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_warn_deserialize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cwl_log_skipped_cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skipped character: {0}, already exists</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -756,15 +796,15 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>工作表缺失对应缺省值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
+      <t>跳过冒险者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: {0},  </t>
     </r>
     <r>
       <rPr>
@@ -773,92 +813,6 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>行3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>或许不兼容此版本</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>this is the last time CWL warns about it, the rest will be silently ignored to reduce log spam</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_warn_empty_default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sheet is missing default entries (3rd row) and might be incompatible</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_warn_stock_file</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_log_post_cleanup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_warn_deserialize</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cwl_log_skipped_cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skipped character: {0}, already exists</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>跳过冒险者</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">: {0},  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
       <t>人物已存在</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -944,10 +898,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>failed to add thing:{0} to {1}, cannot be generated</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>qualified custom {0} id: {1}, type: {2}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -966,30 +916,6 @@
   <si>
     <t>failed to query decltype from mod: {0}, it might've failed to load or is missing (transitive) dependencies
 this is not an exception from CWL and you may ignore it</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>failed to create character {0}, cannot be generated</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>无法生成人物</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15.8"/>
-        <rFont val="Cascadia Code"/>
-        <family val="3"/>
-      </rPr>
-      <t>: {0}</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3847,6 +3773,93 @@
   </si>
   <si>
     <t>忽略并重新生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无法生成人物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+{1}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>failed to create character {0}
+{1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无法添加物品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> {1}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="15.8"/>
+        <rFont val="Cascadia Code"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+{2}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>failed to add thing:{0} to {1}
+{2}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4439,16 +4452,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="4" t="s">
-        <v>154</v>
+      <c r="C6" s="3" t="s">
+        <v>368</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>155</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
@@ -4469,7 +4482,7 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>85</v>
@@ -4528,22 +4541,22 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="9" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
@@ -4552,7 +4565,7 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>88</v>
@@ -4564,7 +4577,7 @@
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>80</v>
@@ -4612,7 +4625,7 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>68</v>
@@ -4624,7 +4637,7 @@
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>69</v>
@@ -4646,7 +4659,7 @@
         <v>62</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>92</v>
@@ -4654,14 +4667,14 @@
     </row>
     <row r="24" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="9" customFormat="1" ht="23.25" x14ac:dyDescent="0.2">
@@ -4670,10 +4683,10 @@
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
@@ -4682,7 +4695,7 @@
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>93</v>
@@ -4694,7 +4707,7 @@
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>70</v>
@@ -4733,7 +4746,7 @@
         <v>40</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
@@ -4814,7 +4827,7 @@
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>100</v>
@@ -4826,7 +4839,7 @@
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>71</v>
@@ -4838,7 +4851,7 @@
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>101</v>
@@ -4856,16 +4869,16 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B41" s="1"/>
-      <c r="C41" s="4" t="s">
-        <v>148</v>
+      <c r="C41" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>105</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
@@ -4894,70 +4907,70 @@
     </row>
     <row r="44" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="93" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="8" customFormat="1" ht="186" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
@@ -4984,886 +4997,886 @@
     </row>
     <row r="52" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B53" s="9"/>
       <c r="C53" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B54" s="9"/>
       <c r="C54" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B55" s="10"/>
       <c r="C55" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="69.75" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B56" s="9"/>
       <c r="C56" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="69.75" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B57" s="10"/>
       <c r="C57" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B58" s="10"/>
       <c r="C58" s="10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B59" s="10"/>
       <c r="C59" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B60" s="10"/>
       <c r="C60" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="D62" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D63" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="69.75" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="17" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B78" s="4"/>
       <c r="C78" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B82" s="4"/>
       <c r="C82" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B85" s="4"/>
       <c r="C85" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B86" s="4"/>
       <c r="C86" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="51" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B87" s="4"/>
       <c r="C87" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B88" s="4"/>
       <c r="C88" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B89" s="4"/>
       <c r="C89" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="69.75" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A95" s="19" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="14" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="18" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="18" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="16" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="18" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B102" s="4"/>
       <c r="C102" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B103" s="4"/>
       <c r="C103" s="18" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="18" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B105" s="4"/>
       <c r="C105" s="14" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A106" s="19" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B106" s="4"/>
       <c r="C106" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="18" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B108" s="4"/>
       <c r="C108" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="69.75" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B111" s="4"/>
       <c r="C111" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B112" s="4"/>
       <c r="C112" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B113" s="4"/>
       <c r="C113" s="14" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="45" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B114" s="4"/>
       <c r="C114" s="14" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D114" s="24" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B115" s="4"/>
       <c r="C115" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="D115" s="16" t="s">
         <v>365</v>
-      </c>
-      <c r="D115" s="16" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B116" s="4"/>
       <c r="C116" s="14" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B117" s="4"/>
       <c r="C117" s="18" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B118" s="4"/>
       <c r="C118" s="14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="14" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A120" s="20" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B120" s="20"/>
       <c r="C120" s="20" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D120" s="20" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B121" s="20"/>
       <c r="C121" s="21" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B122" s="20"/>
       <c r="C122" s="21" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D122" s="22" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="46.5" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B123" s="20"/>
       <c r="C123" s="21" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D123" s="21" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="45.75" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B124" s="20"/>
       <c r="C124" s="21" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D124" s="22" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C125" s="23" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
